--- a/datos/inventario/ECC_Calculations_NUBASE2020.xlsx
+++ b/datos/inventario/ECC_Calculations_NUBASE2020.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="352">
   <si>
     <t xml:space="preserve">Sección transversal efectiva (σ) en barns</t>
   </si>
@@ -348,6 +348,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.2474 d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AF FLiBe 100/100 → 1 (gas noble, KP-TR-012 Tabla B-4)</t>
   </si>
   <si>
     <t xml:space="preserve">Zr-94</t>
@@ -3019,11 +3022,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="73633495"/>
-        <c:axId val="10360489"/>
+        <c:axId val="5052004"/>
+        <c:axId val="49503193"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="73633495"/>
+        <c:axId val="5052004"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3092,7 +3095,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10360489"/>
+        <c:crossAx val="49503193"/>
         <c:crossesAt val="1E-005"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3100,7 +3103,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="10360489"/>
+        <c:axId val="49503193"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -3168,7 +3171,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73633495"/>
+        <c:crossAx val="5052004"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4129,11 +4132,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="11573739"/>
-        <c:axId val="28918306"/>
+        <c:axId val="6439918"/>
+        <c:axId val="94596140"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="11573739"/>
+        <c:axId val="6439918"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4202,7 +4205,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28918306"/>
+        <c:crossAx val="94596140"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4210,7 +4213,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="28918306"/>
+        <c:axId val="94596140"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -4277,7 +4280,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11573739"/>
+        <c:crossAx val="6439918"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5309,11 +5312,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="28687858"/>
-        <c:axId val="83605933"/>
+        <c:axId val="61189325"/>
+        <c:axId val="25553534"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="28687858"/>
+        <c:axId val="61189325"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5382,7 +5385,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83605933"/>
+        <c:crossAx val="25553534"/>
         <c:crossesAt val="1E-008"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5390,7 +5393,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83605933"/>
+        <c:axId val="25553534"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -5457,7 +5460,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28687858"/>
+        <c:crossAx val="61189325"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6376,11 +6379,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="18295185"/>
-        <c:axId val="75956609"/>
+        <c:axId val="99540475"/>
+        <c:axId val="5777554"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="18295185"/>
+        <c:axId val="99540475"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6449,7 +6452,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75956609"/>
+        <c:crossAx val="5777554"/>
         <c:crossesAt val="1E-006"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6457,7 +6460,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="75956609"/>
+        <c:axId val="5777554"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -6524,7 +6527,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18295185"/>
+        <c:crossAx val="99540475"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9013,10 +9016,10 @@
         <v>1</v>
       </c>
       <c r="AF18" s="48" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="AG18" s="48" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="AH18" s="38" t="n">
         <v>1</v>
@@ -9026,15 +9029,15 @@
       </c>
       <c r="AJ18" s="49" t="n">
         <f aca="false">$S18*(1/X18)*(1/Z18)*(1/AB18)*(1/AD18)*(1/AF18)*(1/AH18)</f>
-        <v>5556569217.53903</v>
+        <v>555656921753.903</v>
       </c>
       <c r="AK18" s="49" t="n">
         <f aca="false">$S18*(1/Y18)*(1/AA18)*(1/AC18)*(1/AE18)*(1/AG18)*(1/AI18)</f>
-        <v>111131384350.781</v>
+        <v>11113138435078.1</v>
       </c>
       <c r="AL18" s="49" t="n">
         <f aca="false">AK18*0.000000000027</f>
-        <v>3.00054737747107</v>
+        <v>300.054737747107</v>
       </c>
       <c r="AM18" s="49" t="str">
         <f aca="false">B18</f>
@@ -9062,11 +9065,11 @@
       </c>
       <c r="AT18" s="51" t="n">
         <f aca="false">$S18*(1/X18)*(1/Z18)*(1/AB18)*(1/AD18)*(1/AF18)</f>
-        <v>5556569217.53903</v>
+        <v>555656921753.903</v>
       </c>
       <c r="AU18" s="50" t="n">
         <f aca="false">$S18*(1/X18)*(1/Z18)*(1/AB18)*(1/AD18)*(1/AF18)*(1/AH18)</f>
-        <v>5556569217.53903</v>
+        <v>555656921753.903</v>
       </c>
       <c r="AX18" s="50" t="n">
         <f aca="false">AO18</f>
@@ -9090,22 +9093,25 @@
       </c>
       <c r="BC18" s="50" t="n">
         <f aca="false">BB18*(1/AG18)</f>
-        <v>111131384350.781</v>
+        <v>11113138435078.1</v>
       </c>
       <c r="BD18" s="50" t="n">
         <f aca="false">BC18*(1/AI18)</f>
-        <v>111131384350.781</v>
+        <v>11113138435078.1</v>
       </c>
       <c r="BF18" s="36" t="s">
         <v>91</v>
       </c>
       <c r="BG18" s="0" t="n">
         <v>453375.36</v>
+      </c>
+      <c r="BI18" s="36" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>40094</v>
@@ -9186,7 +9192,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>54135</v>
@@ -9198,13 +9204,13 @@
         <v>5.29262E-008</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H20" s="41" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I20" s="42"/>
       <c r="J20" s="27"/>
@@ -9279,10 +9285,10 @@
         <v>1</v>
       </c>
       <c r="AF20" s="48" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="AG20" s="48" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="AH20" s="38" t="n">
         <v>1</v>
@@ -9292,15 +9298,15 @@
       </c>
       <c r="AJ20" s="49" t="n">
         <f aca="false">$S20*(1/X20)*(1/Z20)*(1/AB20)*(1/AD20)*(1/AF20)*(1/AH20)</f>
-        <v>779270662.848613</v>
+        <v>77927066284.8613</v>
       </c>
       <c r="AK20" s="49" t="n">
         <f aca="false">$S20*(1/Y20)*(1/AA20)*(1/AC20)*(1/AE20)*(1/AG20)*(1/AI20)</f>
-        <v>15585413256.9723</v>
+        <v>1558541325697.23</v>
       </c>
       <c r="AL20" s="49" t="n">
         <f aca="false">AK20*0.000000000027</f>
-        <v>0.420806157938251</v>
+        <v>42.0806157938251</v>
       </c>
       <c r="AM20" s="49" t="str">
         <f aca="false">B20</f>
@@ -9328,11 +9334,11 @@
       </c>
       <c r="AT20" s="51" t="n">
         <f aca="false">$S20*(1/X20)*(1/Z20)*(1/AB20)*(1/AD20)*(1/AF20)</f>
-        <v>779270662.848613</v>
+        <v>77927066284.8613</v>
       </c>
       <c r="AU20" s="50" t="n">
         <f aca="false">$S20*(1/X20)*(1/Z20)*(1/AB20)*(1/AD20)*(1/AF20)*(1/AH20)</f>
-        <v>779270662.848613</v>
+        <v>77927066284.8613</v>
       </c>
       <c r="AX20" s="50" t="n">
         <f aca="false">AO20</f>
@@ -9356,22 +9362,25 @@
       </c>
       <c r="BC20" s="50" t="n">
         <f aca="false">BB20*(1/AG20)</f>
-        <v>15585413256.9723</v>
+        <v>1558541325697.23</v>
       </c>
       <c r="BD20" s="50" t="n">
         <f aca="false">BC20*(1/AI20)</f>
-        <v>15585413256.9723</v>
+        <v>1558541325697.23</v>
       </c>
       <c r="BF20" s="36" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BG20" s="0" t="n">
         <v>32904</v>
+      </c>
+      <c r="BI20" s="36" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C21" s="23" t="n">
         <v>40096</v>
@@ -9447,30 +9456,30 @@
       <c r="AL21" s="35"/>
       <c r="AM21" s="35"/>
       <c r="BF21" s="36" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>53129</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E22" s="37" t="n">
         <v>1.74196E-005</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H22" s="41" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I22" s="42" t="n">
         <v>15700000</v>
@@ -9631,7 +9640,7 @@
         <v>165.693802599008</v>
       </c>
       <c r="BF22" s="36" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG22" s="0" t="n">
         <v>509328786931200</v>
@@ -9639,7 +9648,7 @@
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C23" s="23" t="n">
         <v>42095</v>
@@ -9720,7 +9729,7 @@
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>42097</v>
@@ -9801,7 +9810,7 @@
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>42098</v>
@@ -9882,7 +9891,7 @@
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C26" s="23" t="n">
         <v>42100</v>
@@ -9958,30 +9967,30 @@
       <c r="AL26" s="35"/>
       <c r="AM26" s="35"/>
       <c r="BF26" s="36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C27" s="23" t="n">
         <v>43099</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E27" s="37" t="n">
         <v>0.000135738</v>
       </c>
       <c r="F27" s="37" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G27" s="37" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H27" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I27" s="42" t="n">
         <v>213000</v>
@@ -10142,7 +10151,7 @@
         <v>3290.51272728106</v>
       </c>
       <c r="BF27" s="36" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BG27" s="0" t="n">
         <v>6661667095488</v>
@@ -10150,7 +10159,7 @@
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C28" s="23" t="n">
         <v>44100</v>
@@ -10231,7 +10240,7 @@
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C29" s="23" t="n">
         <v>44101</v>
@@ -10312,7 +10321,7 @@
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C30" s="23" t="n">
         <v>44102</v>
@@ -10393,25 +10402,25 @@
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="22" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C31" s="23" t="n">
         <v>44103</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E31" s="37" t="n">
         <v>2.04804E-005</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H31" s="41" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I31" s="42"/>
       <c r="J31" s="27" t="n">
@@ -10572,7 +10581,7 @@
         <v>975405979.291832</v>
       </c>
       <c r="BF31" s="36" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BG31" s="0" t="n">
         <v>3390768</v>
@@ -10580,7 +10589,7 @@
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="22" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C32" s="23" t="n">
         <v>44104</v>
@@ -10661,25 +10670,25 @@
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="22" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C33" s="23" t="n">
         <v>44106</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E33" s="37" t="n">
         <v>2.6273E-005</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H33" s="41" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I33" s="42"/>
       <c r="J33" s="27" t="n">
@@ -10840,7 +10849,7 @@
         <v>132078337.213248</v>
       </c>
       <c r="BF33" s="36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BG33" s="0" t="n">
         <v>32123520</v>
@@ -10848,7 +10857,7 @@
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C34" s="23" t="n">
         <v>45103</v>
@@ -10929,23 +10938,23 @@
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="22" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C35" s="23" t="n">
         <v>45105</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E35" s="37" t="n">
         <v>4.30968E-007</v>
       </c>
       <c r="F35" s="37"/>
       <c r="G35" s="37" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H35" s="41" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I35" s="42"/>
       <c r="J35" s="27"/>
@@ -11106,7 +11115,7 @@
         <v>547026977.069659</v>
       </c>
       <c r="BF35" s="36" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="BG35" s="0" t="n">
         <v>127227.6</v>
@@ -11114,7 +11123,7 @@
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C36" s="23" t="n">
         <v>46105</v>
@@ -11195,7 +11204,7 @@
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="22" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C37" s="23" t="n">
         <v>46106</v>
@@ -11276,25 +11285,25 @@
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C38" s="23" t="n">
         <v>92235</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E38" s="37" t="n">
         <v>0.00223551</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H38" s="41" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I38" s="59" t="n">
         <v>703800000</v>
@@ -11455,7 +11464,7 @@
         <v>0.812501786310237</v>
       </c>
       <c r="BF38" s="36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BG38" s="0" t="n">
         <v>22216075960320000</v>
@@ -11463,7 +11472,7 @@
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C39" s="23" t="n">
         <v>46108</v>
@@ -11544,7 +11553,7 @@
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C40" s="23" t="n">
         <v>47109</v>
@@ -11625,7 +11634,7 @@
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C41" s="23" t="n">
         <v>52130</v>
@@ -11701,30 +11710,30 @@
       <c r="AL41" s="35"/>
       <c r="AM41" s="35"/>
       <c r="BF41" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C42" s="23" t="n">
         <v>92237</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E42" s="37" t="n">
         <v>2.84647E-006</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H42" s="41" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I42" s="63"/>
       <c r="J42" s="64"/>
@@ -11885,7 +11894,7 @@
         <v>39398119.5869155</v>
       </c>
       <c r="BF42" s="36" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BG42" s="0" t="n">
         <v>583372.8</v>
@@ -11893,7 +11902,7 @@
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C43" s="23" t="n">
         <v>54131</v>
@@ -11974,7 +11983,7 @@
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C44" s="23" t="n">
         <v>54132</v>
@@ -12055,25 +12064,25 @@
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C45" s="23" t="n">
         <v>92238</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E45" s="37" t="n">
         <v>0.0179355</v>
       </c>
       <c r="F45" s="37" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G45" s="37" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H45" s="41" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I45" s="59" t="n">
         <v>4468000000</v>
@@ -12234,7 +12243,7 @@
         <v>1.02826953307641</v>
       </c>
       <c r="BF45" s="36" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BG45" s="0" t="n">
         <v>1.4083856109504E+017</v>
@@ -12242,7 +12251,7 @@
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="22" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C46" s="23" t="n">
         <v>54134</v>
@@ -12323,25 +12332,25 @@
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="22" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C47" s="23" t="n">
         <v>93237</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E47" s="37" t="n">
         <v>3.07925E-005</v>
       </c>
       <c r="F47" s="37" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G47" s="37" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I47" s="59"/>
       <c r="J47" s="27" t="n">
@@ -12502,7 +12511,7 @@
         <v>3.67485777634551</v>
       </c>
       <c r="BF47" s="36" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="BG47" s="0" t="n">
         <v>67658049515520</v>
@@ -12510,7 +12519,7 @@
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="22" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C48" s="23" t="n">
         <v>54136</v>
@@ -12586,12 +12595,12 @@
       <c r="AL48" s="35"/>
       <c r="AM48" s="35"/>
       <c r="BF48" s="36" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="22" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C49" s="23" t="n">
         <v>55133</v>
@@ -12672,7 +12681,7 @@
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="22" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C50" s="23" t="n">
         <v>55134</v>
@@ -12684,13 +12693,13 @@
         <v>1.72686E-005</v>
       </c>
       <c r="F50" s="37" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G50" s="37" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H50" s="22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I50" s="26"/>
       <c r="J50" s="27"/>
@@ -12843,36 +12852,36 @@
         <v>2139722436.40049</v>
       </c>
       <c r="BF50" s="36" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="BG50" s="0" t="n">
         <v>65165052.3552</v>
       </c>
       <c r="BI50" s="36" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C51" s="23" t="n">
         <v>93239</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E51" s="37" t="n">
         <v>1.71895E-005</v>
       </c>
       <c r="F51" s="37" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G51" s="37" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H51" s="41" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I51" s="59"/>
       <c r="J51" s="27"/>
@@ -13033,7 +13042,7 @@
         <v>681850675.2662</v>
       </c>
       <c r="BF51" s="36" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="BG51" s="0" t="n">
         <v>203558.4</v>
@@ -13041,25 +13050,25 @@
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C52" s="23" t="n">
         <v>94238</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E52" s="37" t="n">
         <v>8.29987E-006</v>
       </c>
       <c r="F52" s="37" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G52" s="37" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H52" s="41" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I52" s="59" t="n">
         <v>87.7</v>
@@ -13220,7 +13229,7 @@
         <v>24215.4232033186</v>
       </c>
       <c r="BF52" s="36" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="BG52" s="0" t="n">
         <v>2767542417.216</v>
@@ -13228,25 +13237,25 @@
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="22" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C53" s="23" t="n">
         <v>94239</v>
       </c>
       <c r="D53" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E53" s="37" t="n">
         <v>0.000258547</v>
       </c>
       <c r="F53" s="37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G53" s="37" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H53" s="41" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I53" s="59" t="n">
         <v>24100</v>
@@ -13407,7 +13416,7 @@
         <v>2743.86448959861</v>
       </c>
       <c r="BF53" s="36" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="BG53" s="0" t="n">
         <v>760837487788.8</v>
@@ -13415,25 +13424,25 @@
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C54" s="23" t="n">
         <v>94240</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E54" s="37" t="n">
         <v>7.855E-005</v>
       </c>
       <c r="F54" s="37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G54" s="37" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H54" s="41" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I54" s="59" t="n">
         <v>6560</v>
@@ -13594,7 +13603,7 @@
         <v>3063.34928603926</v>
       </c>
       <c r="BF54" s="36" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="BG54" s="0" t="n">
         <v>207044992010.88</v>
@@ -13602,7 +13611,7 @@
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="22" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C55" s="23" t="n">
         <v>57139</v>
@@ -13683,25 +13692,25 @@
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C56" s="23" t="n">
         <v>94241</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E56" s="37" t="n">
         <v>7.80575E-005</v>
       </c>
       <c r="F56" s="37" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H56" s="41" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I56" s="59" t="n">
         <v>14.3</v>
@@ -13862,7 +13871,7 @@
         <v>1393859.89261286</v>
       </c>
       <c r="BF56" s="36" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BG56" s="0" t="n">
         <v>452179193.80032</v>
@@ -13870,25 +13879,25 @@
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C57" s="23" t="n">
         <v>94242</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E57" s="37" t="n">
         <v>2.86215E-005</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G57" s="37" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H57" s="41" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I57" s="59" t="n">
         <v>375000</v>
@@ -14049,7 +14058,7 @@
         <v>19.5290667374305</v>
       </c>
       <c r="BF57" s="36" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="BG57" s="0" t="n">
         <v>11833847280000</v>
@@ -14057,25 +14066,25 @@
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="22" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C58" s="23" t="n">
         <v>95241</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E58" s="37" t="n">
         <v>6.97773E-007</v>
       </c>
       <c r="F58" s="37" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H58" s="41" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I58" s="59" t="n">
         <v>14.4</v>
@@ -14236,7 +14245,7 @@
         <v>412.712870105851</v>
       </c>
       <c r="BF58" s="36" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="BG58" s="0" t="n">
         <v>13651526222.208</v>
@@ -14244,25 +14253,25 @@
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C59" s="23" t="n">
         <v>95243</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E59" s="37" t="n">
         <v>5.53963E-006</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G59" s="37" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H59" s="41" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I59" s="59"/>
       <c r="J59" s="27"/>
@@ -14423,7 +14432,7 @@
         <v>192.847399166304</v>
       </c>
       <c r="BF59" s="36" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="BG59" s="0" t="n">
         <v>231943406688</v>
@@ -14431,25 +14440,25 @@
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="22" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C60" s="23" t="n">
         <v>38089</v>
       </c>
       <c r="D60" s="23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E60" s="37" t="n">
         <v>2.33352E-005</v>
       </c>
       <c r="F60" s="37" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G60" s="37" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H60" s="22" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I60" s="26"/>
       <c r="J60" s="67" t="n">
@@ -14610,7 +14619,7 @@
         <v>43130054867.596</v>
       </c>
       <c r="BF60" s="36" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="BG60" s="0" t="n">
         <v>4368643.2</v>
@@ -14618,25 +14627,25 @@
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C61" s="23" t="n">
         <v>38090</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E61" s="37" t="n">
         <v>0.000123058</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H61" s="22" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I61" s="26" t="n">
         <v>28.8</v>
@@ -14797,7 +14806,7 @@
         <v>1089136035.42421</v>
       </c>
       <c r="BF61" s="36" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="BG61" s="0" t="n">
         <v>912310732.9728</v>
@@ -14805,13 +14814,13 @@
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C62" s="23" t="n">
         <v>56138</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E62" s="37" t="n">
         <v>0.000167617</v>
@@ -14821,7 +14830,7 @@
         <v>53</v>
       </c>
       <c r="H62" s="41" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I62" s="42" t="n">
         <f aca="false">30.018</f>
@@ -14988,25 +14997,25 @@
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C63" s="23" t="n">
         <v>56140</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E63" s="37" t="n">
         <v>1.10185E-005</v>
       </c>
       <c r="F63" s="37" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G63" s="37" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H63" s="41" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I63" s="42"/>
       <c r="J63" s="27" t="n">
@@ -15167,7 +15176,7 @@
         <v>80741685570.4183</v>
       </c>
       <c r="BF63" s="36" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="BG63" s="0" t="n">
         <v>1101893.76</v>
@@ -15175,23 +15184,23 @@
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C64" s="23" t="n">
         <v>61147</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E64" s="37" t="n">
         <v>2.53495E-005</v>
       </c>
       <c r="F64" s="37"/>
       <c r="G64" s="37" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H64" s="41" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I64" s="59"/>
       <c r="J64" s="27"/>
@@ -15352,34 +15361,34 @@
         <v>2472437090.6092</v>
       </c>
       <c r="BF64" s="36" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="BG64" s="0" t="n">
         <v>82786439.878272</v>
       </c>
       <c r="BH64" s="36" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="69" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C65" s="70" t="n">
         <v>61149</v>
       </c>
       <c r="D65" s="70" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E65" s="71" t="n">
         <v>3.50308E-007</v>
       </c>
       <c r="F65" s="71"/>
       <c r="G65" s="71" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H65" s="72" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I65" s="73"/>
       <c r="J65" s="61"/>
@@ -15540,13 +15549,13 @@
         <v>14802385134.9988</v>
       </c>
       <c r="BF65" s="36" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="BG65" s="0" t="n">
         <v>191088</v>
       </c>
       <c r="BH65" s="36" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15603,25 +15612,25 @@
     </row>
     <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="22" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C67" s="23" t="n">
         <v>39091</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E67" s="37" t="n">
         <v>3.29343E-005</v>
       </c>
       <c r="F67" s="37" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G67" s="37" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H67" s="22" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I67" s="81"/>
       <c r="J67" s="28" t="n">
@@ -15690,7 +15699,7 @@
         <v>Y-91</v>
       </c>
       <c r="BF67" s="36" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="BG67" s="0" t="n">
         <v>5055264</v>
@@ -15698,7 +15707,7 @@
     </row>
     <row r="68" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="82" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C68" s="83" t="n">
         <v>60148</v>
@@ -15779,25 +15788,25 @@
     </row>
     <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C69" s="23" t="n">
         <v>40093</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E69" s="37" t="n">
         <v>0.000143526</v>
       </c>
       <c r="F69" s="37" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G69" s="37" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H69" s="41" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I69" s="42" t="n">
         <v>1530000</v>
@@ -15866,7 +15875,7 @@
         <v>Zr-93</v>
       </c>
       <c r="BF69" s="36" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="BG69" s="0" t="n">
         <v>50806650988800</v>
@@ -15874,25 +15883,25 @@
     </row>
     <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="22" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C70" s="23" t="n">
         <v>40095</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E70" s="37" t="n">
         <v>4.35054E-005</v>
       </c>
       <c r="F70" s="37" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G70" s="37" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H70" s="41" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I70" s="42"/>
       <c r="J70" s="27" t="n">
@@ -15961,7 +15970,7 @@
         <v>Zr-95</v>
       </c>
       <c r="BF70" s="36" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="BG70" s="0" t="n">
         <v>5532364.8</v>
@@ -15969,25 +15978,25 @@
     </row>
     <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="22" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C71" s="23" t="n">
         <v>41095</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E71" s="37" t="n">
         <v>2.02169E-005</v>
       </c>
       <c r="F71" s="37" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G71" s="37" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H71" s="22" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I71" s="26"/>
       <c r="J71" s="27" t="n">
@@ -16056,7 +16065,7 @@
         <v>Nb-95</v>
       </c>
       <c r="BF71" s="36" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="BG71" s="0" t="n">
         <v>3023222.4</v>
@@ -16064,23 +16073,23 @@
     </row>
     <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="22" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C72" s="23" t="n">
         <v>58140</v>
       </c>
       <c r="D72" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E72" s="37" t="n">
         <v>0.000141465</v>
       </c>
       <c r="F72" s="37"/>
       <c r="G72" s="37" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H72" s="41" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I72" s="59"/>
       <c r="J72" s="27"/>
@@ -16152,28 +16161,28 @@
         <v>54</v>
       </c>
       <c r="BH72" s="36" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="22" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C73" s="23" t="n">
         <v>58141</v>
       </c>
       <c r="D73" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E73" s="37" t="n">
         <v>2.33596E-005</v>
       </c>
       <c r="F73" s="37"/>
       <c r="G73" s="37" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H73" s="41" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I73" s="59"/>
       <c r="J73" s="27"/>
@@ -16242,24 +16251,24 @@
         <v>Ce-141</v>
       </c>
       <c r="BF73" s="36" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="BG73" s="0" t="n">
         <v>2808432</v>
       </c>
       <c r="BH73" s="36" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C74" s="23" t="n">
         <v>58142</v>
       </c>
       <c r="D74" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E74" s="37" t="n">
         <v>0.000144249</v>
@@ -16269,7 +16278,7 @@
         <v>53</v>
       </c>
       <c r="H74" s="41" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I74" s="59"/>
       <c r="J74" s="27"/>
@@ -16341,28 +16350,28 @@
         <v>54</v>
       </c>
       <c r="BH74" s="36" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="22" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C75" s="23" t="n">
         <v>58144</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E75" s="37" t="n">
         <v>8.66279E-005</v>
       </c>
       <c r="F75" s="37"/>
       <c r="G75" s="37" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H75" s="41" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I75" s="59"/>
       <c r="J75" s="27"/>
@@ -16431,34 +16440,34 @@
         <v>Ce-144</v>
       </c>
       <c r="BF75" s="36" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="BG75" s="0" t="n">
         <v>24614150.4</v>
       </c>
       <c r="BH75" s="36" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C76" s="23" t="n">
         <v>59141</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E76" s="37" t="n">
         <v>0.000116698</v>
       </c>
       <c r="F76" s="37"/>
       <c r="G76" s="37" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H76" s="41" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I76" s="59"/>
       <c r="J76" s="27"/>
@@ -16530,28 +16539,28 @@
         <v>54</v>
       </c>
       <c r="BH76" s="36" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="22" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C77" s="23" t="n">
         <v>59143</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E77" s="37" t="n">
         <v>1.0667E-005</v>
       </c>
       <c r="F77" s="37"/>
       <c r="G77" s="37" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H77" s="41" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I77" s="59"/>
       <c r="J77" s="27"/>
@@ -16620,24 +16629,24 @@
         <v>Pr-143</v>
       </c>
       <c r="BF77" s="36" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="BG77" s="0" t="n">
         <v>1172448</v>
       </c>
       <c r="BH77" s="36" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C78" s="23" t="n">
         <v>60143</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E78" s="37" t="n">
         <v>0.000100964</v>
@@ -16647,7 +16656,7 @@
         <v>53</v>
       </c>
       <c r="H78" s="41" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I78" s="59"/>
       <c r="J78" s="27"/>
@@ -16721,23 +16730,23 @@
     </row>
     <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C79" s="23" t="n">
         <v>60144</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E79" s="37" t="n">
         <v>7.13987E-005</v>
       </c>
       <c r="F79" s="37"/>
       <c r="G79" s="37" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H79" s="41" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I79" s="59"/>
       <c r="J79" s="27"/>
@@ -16806,12 +16815,12 @@
         <v>Nd-144</v>
       </c>
       <c r="BF79" s="36" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="22" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C80" s="23" t="n">
         <v>64157</v>
@@ -16892,13 +16901,13 @@
     </row>
     <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="22" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C81" s="23" t="n">
         <v>60145</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E81" s="37" t="n">
         <v>8.47874E-005</v>
@@ -16908,7 +16917,7 @@
         <v>53</v>
       </c>
       <c r="H81" s="41" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I81" s="59"/>
       <c r="J81" s="27"/>
@@ -16982,25 +16991,25 @@
     </row>
     <row r="82" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="22" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C82" s="23" t="n">
         <v>92236</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E82" s="37" t="n">
         <v>0.000433584</v>
       </c>
       <c r="F82" s="37" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G82" s="37" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H82" s="41" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I82" s="59"/>
       <c r="J82" s="27"/>
@@ -17153,24 +17162,24 @@
         <v>4.73703641791764</v>
       </c>
       <c r="BF82" s="36" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="BG82" s="0" t="n">
         <v>739063208793600</v>
       </c>
       <c r="BI82" s="36" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="22" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C83" s="23" t="n">
         <v>60146</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E83" s="37" t="n">
         <v>8.23345E-005</v>
@@ -17180,7 +17189,7 @@
         <v>53</v>
       </c>
       <c r="H83" s="41" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I83" s="59"/>
       <c r="J83" s="27" t="n">
@@ -17254,25 +17263,25 @@
     </row>
     <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="22" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C84" s="23" t="n">
         <v>60147</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E84" s="37" t="n">
         <v>3.36571E-006</v>
       </c>
       <c r="F84" s="37" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G84" s="37" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H84" s="41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I84" s="59"/>
       <c r="J84" s="27"/>
@@ -17341,7 +17350,7 @@
         <v>Nd-147</v>
       </c>
       <c r="BF84" s="36" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="BG84" s="0" t="n">
         <v>948672</v>
@@ -17349,13 +17358,13 @@
     </row>
     <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="22" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C85" s="23" t="n">
         <v>60150</v>
       </c>
       <c r="D85" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E85" s="37" t="n">
         <v>1.83824E-005</v>
@@ -17365,7 +17374,7 @@
         <v>53</v>
       </c>
       <c r="H85" s="41" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I85" s="59" t="n">
         <v>7E+018</v>
@@ -17434,30 +17443,30 @@
         <v>Nd-150</v>
       </c>
       <c r="BF85" s="36" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="22" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C86" s="23" t="n">
         <v>62147</v>
       </c>
       <c r="D86" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E86" s="37" t="n">
         <v>3.14028E-006</v>
       </c>
       <c r="F86" s="37" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G86" s="37" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H86" s="41" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I86" s="59"/>
       <c r="J86" s="27"/>
@@ -17526,34 +17535,34 @@
         <v>Sm-147</v>
       </c>
       <c r="BF86" s="36" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="BG86" s="0" t="n">
         <v>3.363968320128E+018</v>
       </c>
       <c r="BH86" s="36" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B87" s="22" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C87" s="23" t="n">
         <v>62149</v>
       </c>
       <c r="D87" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E87" s="37" t="n">
         <v>3.24339E-007</v>
       </c>
       <c r="F87" s="37"/>
       <c r="G87" s="37" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H87" s="41" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I87" s="59"/>
       <c r="J87" s="27"/>
@@ -17625,18 +17634,18 @@
         <v>54</v>
       </c>
       <c r="BH87" s="36" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B88" s="22" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C88" s="23" t="n">
         <v>62150</v>
       </c>
       <c r="D88" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E88" s="37" t="n">
         <v>2.42831E-005</v>
@@ -17646,7 +17655,7 @@
         <v>53</v>
       </c>
       <c r="H88" s="41" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I88" s="59"/>
       <c r="J88" s="27"/>
@@ -17718,28 +17727,28 @@
         <v>54</v>
       </c>
       <c r="BH88" s="36" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B89" s="22" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C89" s="23" t="n">
         <v>62151</v>
       </c>
       <c r="D89" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E89" s="37" t="n">
         <v>1.86627E-006</v>
       </c>
       <c r="F89" s="37"/>
       <c r="G89" s="37" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H89" s="41" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I89" s="59"/>
       <c r="J89" s="27"/>
@@ -17808,24 +17817,24 @@
         <v>Sm-151</v>
       </c>
       <c r="BF89" s="36" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="BG89" s="0" t="n">
         <v>2985285207.168</v>
       </c>
       <c r="BH89" s="36" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B90" s="22" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C90" s="23" t="n">
         <v>62152</v>
       </c>
       <c r="D90" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E90" s="37" t="n">
         <v>1.06573E-005</v>
@@ -17835,7 +17844,7 @@
         <v>53</v>
       </c>
       <c r="H90" s="41" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I90" s="59"/>
       <c r="J90" s="27"/>
@@ -17907,28 +17916,28 @@
         <v>54</v>
       </c>
       <c r="BH90" s="36" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B91" s="22" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C91" s="23" t="n">
         <v>63153</v>
       </c>
       <c r="D91" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E91" s="37" t="n">
         <v>1.08169E-005</v>
       </c>
       <c r="F91" s="37"/>
       <c r="G91" s="37" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H91" s="41" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I91" s="59"/>
       <c r="J91" s="27"/>
@@ -18000,28 +18009,28 @@
         <v>54</v>
       </c>
       <c r="BH91" s="36" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B92" s="22" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C92" s="23" t="n">
         <v>63154</v>
       </c>
       <c r="D92" s="23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E92" s="37" t="n">
         <v>1.93525E-006</v>
       </c>
       <c r="F92" s="37"/>
       <c r="G92" s="37" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H92" s="41" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I92" s="59"/>
       <c r="J92" s="27"/>
@@ -18179,37 +18188,37 @@
         <v>57631931.4353424</v>
       </c>
       <c r="BF92" s="36" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="BG92" s="0" t="n">
         <v>271137108.87936</v>
       </c>
       <c r="BH92" s="36" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="BI92" s="36" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B93" s="22" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C93" s="23" t="n">
         <v>63155</v>
       </c>
       <c r="D93" s="23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E93" s="37" t="n">
         <v>5.7612E-007</v>
       </c>
       <c r="F93" s="37"/>
       <c r="G93" s="37" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H93" s="41" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I93" s="59"/>
       <c r="J93" s="27"/>
@@ -18367,16 +18376,16 @@
         <v>31086495.7822499</v>
       </c>
       <c r="BF93" s="36" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="BG93" s="0" t="n">
         <v>149642943.47136</v>
       </c>
       <c r="BH93" s="36" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="BI93" s="36" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -18384,10 +18393,10 @@
     <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G97" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J97" s="92" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18395,7 +18404,7 @@
         <v>87</v>
       </c>
       <c r="J98" s="92" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K98" s="92" t="n">
         <v>120</v>
@@ -18403,10 +18412,10 @@
     </row>
     <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G99" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J99" s="92" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K99" s="92" t="n">
         <v>309</v>
@@ -18419,7 +18428,7 @@
     </row>
     <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G101" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18429,22 +18438,22 @@
     </row>
     <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G103" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G104" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G105" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G106" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19743,15 +19752,15 @@
         <v>0</v>
       </c>
       <c r="U2" s="98" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="V2" s="98"/>
       <c r="W2" s="98" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="X2" s="98"/>
       <c r="Y2" s="98" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Z2" s="98"/>
       <c r="AA2" s="98" t="s">
@@ -21480,7 +21489,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>40094</v>
@@ -21555,7 +21564,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>54135</v>
@@ -21567,13 +21576,13 @@
         <v>5.29262E-008</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H20" s="41" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I20" s="42"/>
       <c r="J20" s="27"/>
@@ -21706,7 +21715,7 @@
         <v>30559633837.2005</v>
       </c>
       <c r="BF20" s="36" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BG20" s="0" t="n">
         <v>32904</v>
@@ -21714,7 +21723,7 @@
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C21" s="23" t="n">
         <v>40096</v>
@@ -21784,30 +21793,30 @@
       <c r="AF21" s="35"/>
       <c r="AG21" s="35"/>
       <c r="BF21" s="36" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C22" s="23" t="n">
         <v>53129</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E22" s="37" t="n">
         <v>1.74196E-005</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H22" s="41" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I22" s="42" t="n">
         <v>15700000</v>
@@ -21942,7 +21951,7 @@
         <v>6.49779618035325E-007</v>
       </c>
       <c r="BF22" s="36" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BG22" s="0" t="n">
         <v>509328786931200</v>
@@ -21950,7 +21959,7 @@
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C23" s="23" t="n">
         <v>42095</v>
@@ -22025,7 +22034,7 @@
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>42097</v>
@@ -22100,7 +22109,7 @@
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>42098</v>
@@ -22175,7 +22184,7 @@
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C26" s="23" t="n">
         <v>42100</v>
@@ -22245,30 +22254,30 @@
       <c r="AF26" s="35"/>
       <c r="AG26" s="35"/>
       <c r="BF26" s="36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C27" s="23" t="n">
         <v>43099</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E27" s="37" t="n">
         <v>0.000135738</v>
       </c>
       <c r="F27" s="37" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G27" s="37" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H27" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I27" s="42" t="n">
         <v>213000</v>
@@ -22403,7 +22412,7 @@
         <v>2.19367515152071E-006</v>
       </c>
       <c r="BF27" s="36" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BG27" s="0" t="n">
         <v>6661667095488</v>
@@ -22411,7 +22420,7 @@
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C28" s="23" t="n">
         <v>44100</v>
@@ -22486,7 +22495,7 @@
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C29" s="23" t="n">
         <v>44101</v>
@@ -22561,7 +22570,7 @@
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C30" s="23" t="n">
         <v>44102</v>
@@ -22636,25 +22645,25 @@
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="22" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C31" s="23" t="n">
         <v>44103</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E31" s="37" t="n">
         <v>2.04804E-005</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H31" s="41" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I31" s="42"/>
       <c r="J31" s="27" t="n">
@@ -22789,7 +22798,7 @@
         <v>0.650270652861221</v>
       </c>
       <c r="BF31" s="36" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BG31" s="0" t="n">
         <v>3390768</v>
@@ -22797,7 +22806,7 @@
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="22" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C32" s="23" t="n">
         <v>44104</v>
@@ -22872,25 +22881,25 @@
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="22" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C33" s="23" t="n">
         <v>44106</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E33" s="37" t="n">
         <v>2.6273E-005</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H33" s="41" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I33" s="42"/>
       <c r="J33" s="27" t="n">
@@ -23025,7 +23034,7 @@
         <v>0.0880522248088323</v>
       </c>
       <c r="BF33" s="36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BG33" s="0" t="n">
         <v>32123520</v>
@@ -23033,7 +23042,7 @@
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C34" s="23" t="n">
         <v>45103</v>
@@ -23108,23 +23117,23 @@
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="22" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C35" s="23" t="n">
         <v>45105</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E35" s="37" t="n">
         <v>4.30968E-007</v>
       </c>
       <c r="F35" s="37"/>
       <c r="G35" s="37" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H35" s="41" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I35" s="42"/>
       <c r="J35" s="27"/>
@@ -23259,7 +23268,7 @@
         <v>0.364684651379773</v>
       </c>
       <c r="BF35" s="36" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="BG35" s="0" t="n">
         <v>127227.6</v>
@@ -23267,7 +23276,7 @@
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C36" s="23" t="n">
         <v>46105</v>
@@ -23342,7 +23351,7 @@
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="22" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C37" s="23" t="n">
         <v>46106</v>
@@ -23417,25 +23426,25 @@
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C38" s="23" t="n">
         <v>92235</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E38" s="37" t="n">
         <v>0.00223551</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H38" s="41" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I38" s="59" t="n">
         <v>703800000</v>
@@ -23570,7 +23579,7 @@
         <v>9.75002143572285E-010</v>
       </c>
       <c r="BF38" s="36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BG38" s="0" t="n">
         <v>22216075960320000</v>
@@ -23578,7 +23587,7 @@
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C39" s="23" t="n">
         <v>46108</v>
@@ -23653,7 +23662,7 @@
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C40" s="23" t="n">
         <v>47109</v>
@@ -23728,7 +23737,7 @@
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C41" s="23" t="n">
         <v>52130</v>
@@ -23798,30 +23807,30 @@
       <c r="AF41" s="35"/>
       <c r="AG41" s="35"/>
       <c r="BF41" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C42" s="23" t="n">
         <v>92237</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E42" s="37" t="n">
         <v>2.84647E-006</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H42" s="41" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I42" s="63"/>
       <c r="J42" s="64"/>
@@ -23956,7 +23965,7 @@
         <v>0.0472777435042987</v>
       </c>
       <c r="BF42" s="36" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BG42" s="0" t="n">
         <v>583372.8</v>
@@ -23964,7 +23973,7 @@
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C43" s="23" t="n">
         <v>54131</v>
@@ -24039,7 +24048,7 @@
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C44" s="23" t="n">
         <v>54132</v>
@@ -24114,25 +24123,25 @@
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C45" s="23" t="n">
         <v>92238</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E45" s="37" t="n">
         <v>0.0179355</v>
       </c>
       <c r="F45" s="37" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G45" s="37" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H45" s="41" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I45" s="59" t="n">
         <v>4468000000</v>
@@ -24267,7 +24276,7 @@
         <v>1.23392343969169E-009</v>
       </c>
       <c r="BF45" s="36" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BG45" s="0" t="n">
         <v>1.4083856109504E+017</v>
@@ -24275,7 +24284,7 @@
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="22" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C46" s="23" t="n">
         <v>54134</v>
@@ -24350,25 +24359,25 @@
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="22" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C47" s="23" t="n">
         <v>93237</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E47" s="37" t="n">
         <v>3.07925E-005</v>
       </c>
       <c r="F47" s="37" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G47" s="37" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I47" s="59"/>
       <c r="J47" s="27" t="n">
@@ -24503,7 +24512,7 @@
         <v>4.40982933161461E-009</v>
       </c>
       <c r="BF47" s="36" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="BG47" s="0" t="n">
         <v>67658049515520</v>
@@ -24511,7 +24520,7 @@
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="22" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C48" s="23" t="n">
         <v>54136</v>
@@ -24581,12 +24590,12 @@
       <c r="AF48" s="35"/>
       <c r="AG48" s="35"/>
       <c r="BF48" s="36" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="22" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C49" s="23" t="n">
         <v>55133</v>
@@ -24661,7 +24670,7 @@
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="22" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C50" s="23" t="n">
         <v>55134</v>
@@ -24671,13 +24680,13 @@
         <v>1.72686E-005</v>
       </c>
       <c r="F50" s="37" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G50" s="37" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H50" s="22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I50" s="26"/>
       <c r="J50" s="27"/>
@@ -24733,7 +24742,7 @@
       <c r="AF50" s="35"/>
       <c r="AG50" s="35"/>
       <c r="BF50" s="36" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="BG50" s="0" t="n">
         <v>65165052.3552</v>
@@ -24741,25 +24750,25 @@
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C51" s="23" t="n">
         <v>93239</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E51" s="37" t="n">
         <v>1.71895E-005</v>
       </c>
       <c r="F51" s="37" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G51" s="37" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H51" s="41" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I51" s="59"/>
       <c r="J51" s="27"/>
@@ -24894,7 +24903,7 @@
         <v>0.818220810319439</v>
       </c>
       <c r="BF51" s="36" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="BG51" s="0" t="n">
         <v>203558.4</v>
@@ -24902,25 +24911,25 @@
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C52" s="23" t="n">
         <v>94238</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E52" s="37" t="n">
         <v>8.29987E-006</v>
       </c>
       <c r="F52" s="37" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G52" s="37" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H52" s="41" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I52" s="59" t="n">
         <v>87.7</v>
@@ -25055,7 +25064,7 @@
         <v>2.90585078439823E-005</v>
       </c>
       <c r="BF52" s="36" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="BG52" s="0" t="n">
         <v>2767542417.216</v>
@@ -25063,25 +25072,25 @@
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="22" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C53" s="23" t="n">
         <v>94239</v>
       </c>
       <c r="D53" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E53" s="37" t="n">
         <v>0.000258547</v>
       </c>
       <c r="F53" s="37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G53" s="37" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H53" s="41" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I53" s="59" t="n">
         <v>24100</v>
@@ -25216,7 +25225,7 @@
         <v>3.29263738751833E-006</v>
       </c>
       <c r="BF53" s="36" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="BG53" s="0" t="n">
         <v>760837487788.8</v>
@@ -25224,25 +25233,25 @@
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C54" s="23" t="n">
         <v>94240</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E54" s="37" t="n">
         <v>7.855E-005</v>
       </c>
       <c r="F54" s="37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G54" s="37" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H54" s="41" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I54" s="59" t="n">
         <v>6560</v>
@@ -25377,7 +25386,7 @@
         <v>3.67601914324712E-006</v>
       </c>
       <c r="BF54" s="36" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="BG54" s="0" t="n">
         <v>207044992010.88</v>
@@ -25385,7 +25394,7 @@
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="22" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C55" s="23" t="n">
         <v>57139</v>
@@ -25460,25 +25469,25 @@
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C56" s="23" t="n">
         <v>94241</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E56" s="37" t="n">
         <v>7.80575E-005</v>
       </c>
       <c r="F56" s="37" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H56" s="41" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I56" s="59" t="n">
         <v>14.3</v>
@@ -25613,7 +25622,7 @@
         <v>0.00167263187113543</v>
       </c>
       <c r="BF56" s="36" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BG56" s="0" t="n">
         <v>452179193.80032</v>
@@ -25621,25 +25630,25 @@
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C57" s="23" t="n">
         <v>94242</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E57" s="37" t="n">
         <v>2.86215E-005</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G57" s="37" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H57" s="41" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I57" s="59" t="n">
         <v>375000</v>
@@ -25774,7 +25783,7 @@
         <v>2.34348800849165E-008</v>
       </c>
       <c r="BF57" s="36" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="BG57" s="0" t="n">
         <v>11833847280000</v>
@@ -25782,25 +25791,25 @@
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="22" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C58" s="23" t="n">
         <v>95241</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E58" s="37" t="n">
         <v>6.97773E-007</v>
       </c>
       <c r="F58" s="37" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H58" s="41" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I58" s="59" t="n">
         <v>14.4</v>
@@ -25935,7 +25944,7 @@
         <v>4.95255444127022E-007</v>
       </c>
       <c r="BF58" s="36" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="BG58" s="0" t="n">
         <v>13651526222.208</v>
@@ -25943,25 +25952,25 @@
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C59" s="23" t="n">
         <v>95243</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E59" s="37" t="n">
         <v>5.53963E-006</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G59" s="37" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H59" s="41" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I59" s="59"/>
       <c r="J59" s="27"/>
@@ -26096,7 +26105,7 @@
         <v>2.31416878999564E-007</v>
       </c>
       <c r="BF59" s="36" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="BG59" s="0" t="n">
         <v>231943406688</v>
@@ -26104,25 +26113,25 @@
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="22" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C60" s="23" t="n">
         <v>38089</v>
       </c>
       <c r="D60" s="23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E60" s="37" t="n">
         <v>2.33352E-005</v>
       </c>
       <c r="F60" s="37" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G60" s="37" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H60" s="22" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I60" s="26"/>
       <c r="J60" s="67" t="n">
@@ -26255,7 +26264,7 @@
         <v>43130.054867596</v>
       </c>
       <c r="BF60" s="36" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="BG60" s="0" t="n">
         <v>4368643.2</v>
@@ -26263,25 +26272,25 @@
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C61" s="23" t="n">
         <v>38090</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E61" s="37" t="n">
         <v>0.000123058</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H61" s="22" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I61" s="26" t="n">
         <v>28.8</v>
@@ -26414,7 +26423,7 @@
         <v>1089.13603542421</v>
       </c>
       <c r="BF61" s="36" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="BG61" s="0" t="n">
         <v>912310732.9728</v>
@@ -26422,13 +26431,13 @@
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C62" s="23" t="n">
         <v>56138</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E62" s="37" t="n">
         <v>0.000167617</v>
@@ -26438,7 +26447,7 @@
         <v>53</v>
       </c>
       <c r="H62" s="41" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I62" s="42" t="n">
         <f aca="false">30.018</f>
@@ -26577,25 +26586,25 @@
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="22" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C63" s="23" t="n">
         <v>56140</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E63" s="37" t="n">
         <v>1.10185E-005</v>
       </c>
       <c r="F63" s="37" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G63" s="37" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H63" s="41" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I63" s="42"/>
       <c r="J63" s="27" t="n">
@@ -26728,7 +26737,7 @@
         <v>80741.6855704183</v>
       </c>
       <c r="BF63" s="36" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="BG63" s="0" t="n">
         <v>1101893.76</v>
@@ -26736,23 +26745,23 @@
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C64" s="23" t="n">
         <v>61147</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E64" s="37" t="n">
         <v>2.53495E-005</v>
       </c>
       <c r="F64" s="37"/>
       <c r="G64" s="37" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H64" s="41" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I64" s="59"/>
       <c r="J64" s="27"/>
@@ -26885,34 +26894,34 @@
         <v>2472.4370906092</v>
       </c>
       <c r="BF64" s="36" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="BG64" s="0" t="n">
         <v>82786439.878272</v>
       </c>
       <c r="BH64" s="36" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="22" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C65" s="23" t="n">
         <v>61149</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E65" s="37" t="n">
         <v>3.50308E-007</v>
       </c>
       <c r="F65" s="37"/>
       <c r="G65" s="37" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H65" s="41" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I65" s="59"/>
       <c r="J65" s="27"/>
@@ -27045,36 +27054,36 @@
         <v>14802.3851349988</v>
       </c>
       <c r="BF65" s="36" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="BG65" s="0" t="n">
         <v>191088</v>
       </c>
       <c r="BH65" s="36" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="22" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C66" s="23" t="n">
         <v>39091</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E66" s="37" t="n">
         <v>3.29343E-005</v>
       </c>
       <c r="F66" s="37" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G66" s="37" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H66" s="22" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I66" s="26"/>
       <c r="J66" s="27" t="n">
@@ -27137,7 +27146,7 @@
         <v>Y-91</v>
       </c>
       <c r="BF66" s="36" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="BG66" s="0" t="n">
         <v>5055264</v>
@@ -27145,7 +27154,7 @@
     </row>
     <row r="67" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="22" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C67" s="23" t="n">
         <v>60148</v>
@@ -27220,25 +27229,25 @@
     </row>
     <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C68" s="23" t="n">
         <v>40093</v>
       </c>
       <c r="D68" s="23" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E68" s="37" t="n">
         <v>0.000143526</v>
       </c>
       <c r="F68" s="37" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G68" s="37" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H68" s="41" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I68" s="42" t="n">
         <v>1530000</v>
@@ -27301,7 +27310,7 @@
         <v>Zr-93</v>
       </c>
       <c r="BF68" s="36" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="BG68" s="0" t="n">
         <v>50806650988800</v>
@@ -27309,25 +27318,25 @@
     </row>
     <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="22" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C69" s="23" t="n">
         <v>40095</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E69" s="37" t="n">
         <v>4.35054E-005</v>
       </c>
       <c r="F69" s="37" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G69" s="37" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H69" s="41" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I69" s="42"/>
       <c r="J69" s="27" t="n">
@@ -27390,7 +27399,7 @@
         <v>Zr-95</v>
       </c>
       <c r="BF69" s="36" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="BG69" s="0" t="n">
         <v>5532364.8</v>
@@ -27398,25 +27407,25 @@
     </row>
     <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="22" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C70" s="23" t="n">
         <v>41095</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E70" s="37" t="n">
         <v>2.02169E-005</v>
       </c>
       <c r="F70" s="37" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G70" s="37" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H70" s="22" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I70" s="26"/>
       <c r="J70" s="27" t="n">
@@ -27479,7 +27488,7 @@
         <v>Nb-95</v>
       </c>
       <c r="BF70" s="36" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="BG70" s="0" t="n">
         <v>3023222.4</v>
@@ -27487,23 +27496,23 @@
     </row>
     <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="22" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C71" s="23" t="n">
         <v>58140</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E71" s="37" t="n">
         <v>0.000141465</v>
       </c>
       <c r="F71" s="37"/>
       <c r="G71" s="37" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H71" s="41" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I71" s="59"/>
       <c r="J71" s="27"/>
@@ -27569,28 +27578,28 @@
         <v>54</v>
       </c>
       <c r="BH71" s="36" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="22" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C72" s="23" t="n">
         <v>58141</v>
       </c>
       <c r="D72" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E72" s="37" t="n">
         <v>2.33596E-005</v>
       </c>
       <c r="F72" s="37"/>
       <c r="G72" s="37" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H72" s="41" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I72" s="59"/>
       <c r="J72" s="27"/>
@@ -27653,24 +27662,24 @@
         <v>Ce-141</v>
       </c>
       <c r="BF72" s="36" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="BG72" s="0" t="n">
         <v>2808432</v>
       </c>
       <c r="BH72" s="36" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C73" s="23" t="n">
         <v>58142</v>
       </c>
       <c r="D73" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E73" s="37" t="n">
         <v>0.000144249</v>
@@ -27680,7 +27689,7 @@
         <v>53</v>
       </c>
       <c r="H73" s="41" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I73" s="59"/>
       <c r="J73" s="27"/>
@@ -27746,28 +27755,28 @@
         <v>54</v>
       </c>
       <c r="BH73" s="36" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="22" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C74" s="23" t="n">
         <v>58144</v>
       </c>
       <c r="D74" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E74" s="37" t="n">
         <v>8.66279E-005</v>
       </c>
       <c r="F74" s="37"/>
       <c r="G74" s="37" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H74" s="41" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I74" s="59"/>
       <c r="J74" s="27"/>
@@ -27830,34 +27839,34 @@
         <v>Ce-144</v>
       </c>
       <c r="BF74" s="36" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="BG74" s="0" t="n">
         <v>24614150.4</v>
       </c>
       <c r="BH74" s="36" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C75" s="23" t="n">
         <v>59141</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E75" s="37" t="n">
         <v>0.000116698</v>
       </c>
       <c r="F75" s="37"/>
       <c r="G75" s="37" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H75" s="41" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I75" s="59"/>
       <c r="J75" s="27"/>
@@ -27923,28 +27932,28 @@
         <v>54</v>
       </c>
       <c r="BH75" s="36" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="22" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C76" s="23" t="n">
         <v>59143</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E76" s="37" t="n">
         <v>1.0667E-005</v>
       </c>
       <c r="F76" s="37"/>
       <c r="G76" s="37" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H76" s="41" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I76" s="59"/>
       <c r="J76" s="27"/>
@@ -28007,24 +28016,24 @@
         <v>Pr-143</v>
       </c>
       <c r="BF76" s="36" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="BG76" s="0" t="n">
         <v>1172448</v>
       </c>
       <c r="BH76" s="36" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C77" s="23" t="n">
         <v>60143</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E77" s="37" t="n">
         <v>0.000100964</v>
@@ -28034,7 +28043,7 @@
         <v>53</v>
       </c>
       <c r="H77" s="41" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I77" s="59"/>
       <c r="J77" s="27"/>
@@ -28102,23 +28111,23 @@
     </row>
     <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C78" s="23" t="n">
         <v>60144</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E78" s="37" t="n">
         <v>7.13987E-005</v>
       </c>
       <c r="F78" s="37"/>
       <c r="G78" s="37" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H78" s="41" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I78" s="59"/>
       <c r="J78" s="27"/>
@@ -28181,12 +28190,12 @@
         <v>Nd-144</v>
       </c>
       <c r="BF78" s="36" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="22" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C79" s="23" t="n">
         <v>64157</v>
@@ -28261,13 +28270,13 @@
     </row>
     <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="22" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C80" s="23" t="n">
         <v>60145</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E80" s="37" t="n">
         <v>8.47874E-005</v>
@@ -28277,7 +28286,7 @@
         <v>53</v>
       </c>
       <c r="H80" s="41" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I80" s="59"/>
       <c r="J80" s="27"/>
@@ -28345,7 +28354,7 @@
     </row>
     <row r="81" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="22" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C81" s="23" t="n">
         <v>92236</v>
@@ -28355,13 +28364,13 @@
         <v>0.000433584</v>
       </c>
       <c r="F81" s="37" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G81" s="37" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H81" s="41" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I81" s="59"/>
       <c r="J81" s="27"/>
@@ -28417,7 +28426,7 @@
       <c r="AF81" s="35"/>
       <c r="AG81" s="35"/>
       <c r="BF81" s="36" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="BG81" s="0" t="n">
         <v>739063208793600</v>
@@ -28425,13 +28434,13 @@
     </row>
     <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="22" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C82" s="23" t="n">
         <v>60146</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E82" s="37" t="n">
         <v>8.23345E-005</v>
@@ -28441,7 +28450,7 @@
         <v>53</v>
       </c>
       <c r="H82" s="41" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I82" s="59"/>
       <c r="J82" s="27" t="n">
@@ -28509,25 +28518,25 @@
     </row>
     <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="22" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C83" s="23" t="n">
         <v>60147</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E83" s="37" t="n">
         <v>3.36571E-006</v>
       </c>
       <c r="F83" s="37" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G83" s="37" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H83" s="41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I83" s="59"/>
       <c r="J83" s="27"/>
@@ -28590,7 +28599,7 @@
         <v>Nd-147</v>
       </c>
       <c r="BF83" s="36" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="BG83" s="0" t="n">
         <v>948672</v>
@@ -28598,13 +28607,13 @@
     </row>
     <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="22" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C84" s="23" t="n">
         <v>60150</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E84" s="37" t="n">
         <v>1.83824E-005</v>
@@ -28614,7 +28623,7 @@
         <v>53</v>
       </c>
       <c r="H84" s="41" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I84" s="59" t="n">
         <v>7E+018</v>
@@ -28677,30 +28686,30 @@
         <v>Nd-150</v>
       </c>
       <c r="BF84" s="36" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="22" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C85" s="23" t="n">
         <v>62147</v>
       </c>
       <c r="D85" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E85" s="37" t="n">
         <v>3.14028E-006</v>
       </c>
       <c r="F85" s="37" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G85" s="37" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H85" s="41" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I85" s="59"/>
       <c r="J85" s="27"/>
@@ -28763,34 +28772,34 @@
         <v>Sm-147</v>
       </c>
       <c r="BF85" s="36" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="BG85" s="0" t="n">
         <v>3.363968320128E+018</v>
       </c>
       <c r="BH85" s="36" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="22" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C86" s="23" t="n">
         <v>62149</v>
       </c>
       <c r="D86" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E86" s="37" t="n">
         <v>3.24339E-007</v>
       </c>
       <c r="F86" s="37"/>
       <c r="G86" s="37" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H86" s="41" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I86" s="59"/>
       <c r="J86" s="27"/>
@@ -28856,18 +28865,18 @@
         <v>54</v>
       </c>
       <c r="BH86" s="36" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B87" s="22" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C87" s="23" t="n">
         <v>62150</v>
       </c>
       <c r="D87" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E87" s="37" t="n">
         <v>2.42831E-005</v>
@@ -28877,7 +28886,7 @@
         <v>53</v>
       </c>
       <c r="H87" s="41" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I87" s="59"/>
       <c r="J87" s="27"/>
@@ -28943,28 +28952,28 @@
         <v>54</v>
       </c>
       <c r="BH87" s="36" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B88" s="22" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C88" s="23" t="n">
         <v>62151</v>
       </c>
       <c r="D88" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E88" s="37" t="n">
         <v>1.86627E-006</v>
       </c>
       <c r="F88" s="37"/>
       <c r="G88" s="37" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H88" s="41" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I88" s="59"/>
       <c r="J88" s="27"/>
@@ -29027,24 +29036,24 @@
         <v>Sm-151</v>
       </c>
       <c r="BF88" s="36" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="BG88" s="0" t="n">
         <v>2985285207.168</v>
       </c>
       <c r="BH88" s="36" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B89" s="22" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C89" s="23" t="n">
         <v>62152</v>
       </c>
       <c r="D89" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E89" s="37" t="n">
         <v>1.06573E-005</v>
@@ -29054,7 +29063,7 @@
         <v>53</v>
       </c>
       <c r="H89" s="41" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I89" s="59"/>
       <c r="J89" s="27"/>
@@ -29120,28 +29129,28 @@
         <v>54</v>
       </c>
       <c r="BH89" s="36" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B90" s="22" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C90" s="23" t="n">
         <v>63153</v>
       </c>
       <c r="D90" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E90" s="37" t="n">
         <v>1.08169E-005</v>
       </c>
       <c r="F90" s="37"/>
       <c r="G90" s="37" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H90" s="41" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I90" s="59"/>
       <c r="J90" s="27"/>
@@ -29207,28 +29216,28 @@
         <v>54</v>
       </c>
       <c r="BH90" s="36" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B91" s="22" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C91" s="23" t="n">
         <v>63154</v>
       </c>
       <c r="D91" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E91" s="37" t="n">
         <v>1.93525E-006</v>
       </c>
       <c r="F91" s="37"/>
       <c r="G91" s="37" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H91" s="41" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I91" s="59"/>
       <c r="J91" s="27"/>
@@ -29291,34 +29300,34 @@
         <v>Eu-154</v>
       </c>
       <c r="BF91" s="36" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="BG91" s="0" t="n">
         <v>271137108.87936</v>
       </c>
       <c r="BH91" s="36" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B92" s="22" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C92" s="23" t="n">
         <v>63155</v>
       </c>
       <c r="D92" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E92" s="37" t="n">
         <v>5.7612E-007</v>
       </c>
       <c r="F92" s="37"/>
       <c r="G92" s="37" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H92" s="41" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I92" s="59"/>
       <c r="J92" s="27"/>
@@ -29381,13 +29390,13 @@
         <v>Eu-155</v>
       </c>
       <c r="BF92" s="36" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="BG92" s="0" t="n">
         <v>149642943.47136</v>
       </c>
       <c r="BH92" s="36" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -29395,10 +29404,10 @@
     <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G96" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J96" s="92" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29406,7 +29415,7 @@
         <v>87</v>
       </c>
       <c r="J97" s="92" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K97" s="92" t="n">
         <v>120</v>
@@ -29414,10 +29423,10 @@
     </row>
     <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G98" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J98" s="92" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K98" s="92" t="n">
         <v>309</v>
@@ -29430,7 +29439,7 @@
     </row>
     <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G100" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29440,22 +29449,22 @@
     </row>
     <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G102" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G103" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G104" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G105" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
